--- a/testdata/payroll-validation/1_configuration.xlsx
+++ b/testdata/payroll-validation/1_configuration.xlsx
@@ -885,21 +885,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
-    <col width="25" customWidth="1" min="8" max="8"/>
-    <col width="28" customWidth="1" min="9" max="9"/>
-    <col width="31" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="31" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -925,40 +926,45 @@
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
+          <t>pf_on_code_wages</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
           <t>esic_employee_rate</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>esic_wage_ceiling</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>esic_rounding</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>esic_employee_formula</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>esic_full_month_on_entry</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>esic_continue_month_on_exit</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>pt_states</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>lwf_states</t>
         </is>
@@ -985,31 +991,27 @@
           <t>MIN((basic + special_allowance) * 12%, 3000)</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
         <is>
           <t>0.0075</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>21000</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>up</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>IF(esic_wage &lt;= 21000, ROUNDUP(esic_wage * 0.75%, 0), 0)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1017,10 +1019,15 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t>Karnataka, Maharashtra</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
